--- a/portfolio_tracker.xlsx
+++ b/portfolio_tracker.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,6 +497,36 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1318.6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1204.13</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1318.6</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/portfolio_tracker.xlsx
+++ b/portfolio_tracker.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,6 +530,246 @@
         <v>0</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>522.4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>476.51</v>
+      </c>
+      <c r="F4" t="n">
+        <v>522.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ESCORTS</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3009.9</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2834.55</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3009.9</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1318.6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1204.13</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1318.6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>IEX</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>132.11</v>
+      </c>
+      <c r="E7" t="n">
+        <v>120.37</v>
+      </c>
+      <c r="F7" t="n">
+        <v>132.11</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>KFINTECH</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>973.75</v>
+      </c>
+      <c r="E8" t="n">
+        <v>875.53</v>
+      </c>
+      <c r="F8" t="n">
+        <v>973.75</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PFIZER</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>4710.7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4412.29</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4710.7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SAGILITY</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>43.16</v>
+      </c>
+      <c r="E10" t="n">
+        <v>38.48</v>
+      </c>
+      <c r="F10" t="n">
+        <v>43.16</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4144.6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3836.31</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4144.6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/portfolio_tracker.xlsx
+++ b/portfolio_tracker.xlsx
@@ -7,17 +7,23 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Positions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Positions'!$A$1:$U$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="+0.00%;-0.00%"/>
+  </numFmts>
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,16 +34,126 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0078350F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E1B4B"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0078350F"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="20"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003730A3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE68A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0010B981"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006366F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -51,14 +167,90 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,6 +617,134 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="B2:G12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>4PM Swing — Portfolio Dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Last updated: 29 Jul 2026, 09:08 AM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>OPEN POSITIONS</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>EXITED (TOTAL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="B6" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>WIN RATE</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>AVG P&amp;L (EXITED)</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>BEST TRADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>WORST TRADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F8:G8"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -773,4 +1093,369 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Serial No</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Signal Date</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Entry Type</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Signal Close (Rs)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>ATR @ Signal</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Entry Date</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Entry Price (Rs)</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Initial Stop (3xATR)</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Current Price (Rs)</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Highest Close Since Entry</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Current Trailing Stop</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>20 SMA (Latest)</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>P&amp;L %</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Exit Date</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>Exit Price (Rs)</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>Exit Reason</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>Days Held</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>Last Updated (IST)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>522.4</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="5" t="n">
+        <v>476.51</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>522.4</v>
+      </c>
+      <c r="L2" s="5" t="inlineStr"/>
+      <c r="M2" s="5" t="inlineStr"/>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="6" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr"/>
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr"/>
+      <c r="T2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>29/07/2026 09:08 AM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>IEX</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>132.11</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="H3" s="7" t="inlineStr"/>
+      <c r="I3" s="8" t="inlineStr"/>
+      <c r="J3" s="8" t="n">
+        <v>120.37</v>
+      </c>
+      <c r="K3" s="8" t="n">
+        <v>132.11</v>
+      </c>
+      <c r="L3" s="8" t="inlineStr"/>
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="inlineStr"/>
+      <c r="P3" s="9" t="inlineStr"/>
+      <c r="Q3" s="7" t="inlineStr"/>
+      <c r="R3" s="7" t="inlineStr"/>
+      <c r="S3" s="7" t="inlineStr"/>
+      <c r="T3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>29/07/2026 09:08 AM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>PFIZER</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>4710.7</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>99.47</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="n">
+        <v>4412.29</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>4710.7</v>
+      </c>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="6" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>29/07/2026 09:08 AM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>SWIGGY</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>268.47</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="n">
+        <v>235.8</v>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v>268.47</v>
+      </c>
+      <c r="L5" s="8" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="9" t="inlineStr"/>
+      <c r="Q5" s="7" t="inlineStr"/>
+      <c r="R5" s="7" t="inlineStr"/>
+      <c r="S5" s="7" t="inlineStr"/>
+      <c r="T5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>29/07/2026 09:08 AM IST</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:U1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/portfolio_tracker.xlsx
+++ b/portfolio_tracker.xlsx
@@ -185,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -250,6 +250,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -638,7 +644,7 @@
     <row r="3">
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Last updated: 29 Jul 2026, 09:08 AM IST</t>
+          <t>Last updated: 29 Jul 2026, 09:29 AM IST</t>
         </is>
       </c>
     </row>
@@ -661,10 +667,10 @@
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="B6" s="15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F6" s="17" t="n">
         <v>0</v>
@@ -1253,9 +1259,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>PENDING ENTRY</t>
+      <c r="E2" s="24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F2" s="5" t="n">
@@ -1264,19 +1270,33 @@
       <c r="G2" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>525</v>
+      </c>
       <c r="J2" s="5" t="n">
-        <v>476.51</v>
+        <v>479.1</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>522.4</v>
-      </c>
-      <c r="L2" s="5" t="inlineStr"/>
-      <c r="M2" s="5" t="inlineStr"/>
+        <v>525</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>525</v>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>479.1</v>
+      </c>
       <c r="N2" s="5" t="inlineStr"/>
-      <c r="O2" s="5" t="inlineStr"/>
-      <c r="P2" s="6" t="inlineStr"/>
+      <c r="O2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q2" s="3" t="inlineStr"/>
       <c r="R2" s="3" t="inlineStr"/>
       <c r="S2" s="3" t="inlineStr"/>
@@ -1285,7 +1305,7 @@
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026 09:08 AM IST</t>
+          <t>29/07/2026 09:25 AM IST</t>
         </is>
       </c>
     </row>
@@ -1308,9 +1328,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>PENDING ENTRY</t>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F3" s="8" t="n">
@@ -1319,19 +1339,33 @@
       <c r="G3" s="7" t="n">
         <v>3.91</v>
       </c>
-      <c r="H3" s="7" t="inlineStr"/>
-      <c r="I3" s="8" t="inlineStr"/>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>132.96</v>
+      </c>
       <c r="J3" s="8" t="n">
-        <v>120.37</v>
+        <v>121.23</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>132.11</v>
-      </c>
-      <c r="L3" s="8" t="inlineStr"/>
-      <c r="M3" s="8" t="inlineStr"/>
+        <v>132.96</v>
+      </c>
+      <c r="L3" s="8" t="n">
+        <v>132.96</v>
+      </c>
+      <c r="M3" s="8" t="n">
+        <v>121.23</v>
+      </c>
       <c r="N3" s="8" t="inlineStr"/>
-      <c r="O3" s="8" t="inlineStr"/>
-      <c r="P3" s="9" t="inlineStr"/>
+      <c r="O3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q3" s="7" t="inlineStr"/>
       <c r="R3" s="7" t="inlineStr"/>
       <c r="S3" s="7" t="inlineStr"/>
@@ -1340,7 +1374,7 @@
       </c>
       <c r="U3" s="7" t="inlineStr">
         <is>
-          <t>29/07/2026 09:08 AM IST</t>
+          <t>29/07/2026 09:25 AM IST</t>
         </is>
       </c>
     </row>
@@ -1363,9 +1397,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>PENDING ENTRY</t>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
@@ -1374,19 +1408,33 @@
       <c r="G4" s="3" t="n">
         <v>99.47</v>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>4735</v>
+      </c>
       <c r="J4" s="5" t="n">
-        <v>4412.29</v>
+        <v>4436.59</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4710.7</v>
-      </c>
-      <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr"/>
+        <v>4735</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>4735</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>4436.59</v>
+      </c>
       <c r="N4" s="5" t="inlineStr"/>
-      <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="6" t="inlineStr"/>
+      <c r="O4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q4" s="3" t="inlineStr"/>
       <c r="R4" s="3" t="inlineStr"/>
       <c r="S4" s="3" t="inlineStr"/>
@@ -1395,7 +1443,7 @@
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026 09:08 AM IST</t>
+          <t>29/07/2026 09:25 AM IST</t>
         </is>
       </c>
     </row>

--- a/portfolio_tracker.xlsx
+++ b/portfolio_tracker.xlsx
@@ -644,7 +644,7 @@
     <row r="3">
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Last updated: 29 Jul 2026, 09:29 AM IST</t>
+          <t>Last updated: 29 Jul 2026, 06:07 PM IST</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="B6" s="15" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D6" s="16" t="n">
         <v>3</v>
@@ -1107,7 +1107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1282,20 +1282,22 @@
         <v>479.1</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>525</v>
+        <v>525.8499755859375</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>525</v>
+        <v>525.8499755859375</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>479.1</v>
-      </c>
-      <c r="N2" s="5" t="inlineStr"/>
+        <v>480.11</v>
+      </c>
+      <c r="N2" s="5" t="n">
+        <v>485.4</v>
+      </c>
       <c r="O2" s="5" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="P2" s="25" t="n">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
       <c r="Q2" s="3" t="inlineStr"/>
       <c r="R2" s="3" t="inlineStr"/>
@@ -1305,7 +1307,7 @@
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026 09:25 AM IST</t>
+          <t>29/07/2026 06:03 PM IST</t>
         </is>
       </c>
     </row>
@@ -1351,20 +1353,22 @@
         <v>121.23</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>132.96</v>
+        <v>134.1900024414062</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>132.96</v>
+        <v>134.1900024414062</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>121.23</v>
-      </c>
-      <c r="N3" s="8" t="inlineStr"/>
+        <v>122.26</v>
+      </c>
+      <c r="N3" s="8" t="n">
+        <v>123.15</v>
+      </c>
       <c r="O3" s="8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P3" s="25" t="n">
-        <v>0</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="Q3" s="7" t="inlineStr"/>
       <c r="R3" s="7" t="inlineStr"/>
@@ -1374,7 +1378,7 @@
       </c>
       <c r="U3" s="7" t="inlineStr">
         <is>
-          <t>29/07/2026 09:25 AM IST</t>
+          <t>29/07/2026 06:03 PM IST</t>
         </is>
       </c>
     </row>
@@ -1420,20 +1424,22 @@
         <v>4436.59</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4735</v>
+        <v>4755.10009765625</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>4735</v>
+        <v>4755.10009765625</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>4436.59</v>
-      </c>
-      <c r="N4" s="5" t="inlineStr"/>
+        <v>4454.29</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>4589.38</v>
+      </c>
       <c r="O4" s="5" t="n">
-        <v>0</v>
+        <v>20.1</v>
       </c>
       <c r="P4" s="25" t="n">
-        <v>0</v>
+        <v>0.0042</v>
       </c>
       <c r="Q4" s="3" t="inlineStr"/>
       <c r="R4" s="3" t="inlineStr"/>
@@ -1443,7 +1449,7 @@
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026 09:25 AM IST</t>
+          <t>29/07/2026 06:03 PM IST</t>
         </is>
       </c>
     </row>
@@ -1502,6 +1508,941 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>AMBUJACEM</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>435.3</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="n">
+        <v>402.34</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>435.3</v>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="6" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>29/07/2026 06:07 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>BAJAJHFL</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>87.63</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr"/>
+      <c r="J7" s="8" t="n">
+        <v>83.52</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>87.63</v>
+      </c>
+      <c r="L7" s="8" t="inlineStr"/>
+      <c r="M7" s="8" t="inlineStr"/>
+      <c r="N7" s="8" t="inlineStr"/>
+      <c r="O7" s="8" t="inlineStr"/>
+      <c r="P7" s="9" t="inlineStr"/>
+      <c r="Q7" s="7" t="inlineStr"/>
+      <c r="R7" s="7" t="inlineStr"/>
+      <c r="S7" s="7" t="inlineStr"/>
+      <c r="T7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="7" t="inlineStr">
+        <is>
+          <t>29/07/2026 06:07 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>5517.5</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="n">
+        <v>5218.25</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>5517.5</v>
+      </c>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="6" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>29/07/2026 06:07 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>264.25</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="H9" s="7" t="inlineStr"/>
+      <c r="I9" s="8" t="inlineStr"/>
+      <c r="J9" s="8" t="n">
+        <v>243.07</v>
+      </c>
+      <c r="K9" s="8" t="n">
+        <v>264.25</v>
+      </c>
+      <c r="L9" s="8" t="inlineStr"/>
+      <c r="M9" s="8" t="inlineStr"/>
+      <c r="N9" s="8" t="inlineStr"/>
+      <c r="O9" s="8" t="inlineStr"/>
+      <c r="P9" s="9" t="inlineStr"/>
+      <c r="Q9" s="7" t="inlineStr"/>
+      <c r="R9" s="7" t="inlineStr"/>
+      <c r="S9" s="7" t="inlineStr"/>
+      <c r="T9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="7" t="inlineStr">
+        <is>
+          <t>29/07/2026 06:07 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>DOMS</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2280.4</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>55.59</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="n">
+        <v>2113.64</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>2280.4</v>
+      </c>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="6" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>29/07/2026 06:07 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>DEVYANI</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>118.36</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="H11" s="7" t="inlineStr"/>
+      <c r="I11" s="8" t="inlineStr"/>
+      <c r="J11" s="8" t="n">
+        <v>107.63</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>118.36</v>
+      </c>
+      <c r="L11" s="8" t="inlineStr"/>
+      <c r="M11" s="8" t="inlineStr"/>
+      <c r="N11" s="8" t="inlineStr"/>
+      <c r="O11" s="8" t="inlineStr"/>
+      <c r="P11" s="9" t="inlineStr"/>
+      <c r="Q11" s="7" t="inlineStr"/>
+      <c r="R11" s="7" t="inlineStr"/>
+      <c r="S11" s="7" t="inlineStr"/>
+      <c r="T11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="7" t="inlineStr">
+        <is>
+          <t>29/07/2026 06:07 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>ESCORTS</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3016.8</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>59.31</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="n">
+        <v>2838.88</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>3016.8</v>
+      </c>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="6" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr"/>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>29/07/2026 06:07 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>2261.7</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="H13" s="7" t="inlineStr"/>
+      <c r="I13" s="8" t="inlineStr"/>
+      <c r="J13" s="8" t="n">
+        <v>2112.06</v>
+      </c>
+      <c r="K13" s="8" t="n">
+        <v>2261.7</v>
+      </c>
+      <c r="L13" s="8" t="inlineStr"/>
+      <c r="M13" s="8" t="inlineStr"/>
+      <c r="N13" s="8" t="inlineStr"/>
+      <c r="O13" s="8" t="inlineStr"/>
+      <c r="P13" s="9" t="inlineStr"/>
+      <c r="Q13" s="7" t="inlineStr"/>
+      <c r="R13" s="7" t="inlineStr"/>
+      <c r="S13" s="7" t="inlineStr"/>
+      <c r="T13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="7" t="inlineStr">
+        <is>
+          <t>29/07/2026 06:07 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>5149.1</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>99.55</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="n">
+        <v>4850.44</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>5149.1</v>
+      </c>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="6" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>29/07/2026 06:07 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>JIOFIN</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>249.48</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="H15" s="7" t="inlineStr"/>
+      <c r="I15" s="8" t="inlineStr"/>
+      <c r="J15" s="8" t="n">
+        <v>230.33</v>
+      </c>
+      <c r="K15" s="8" t="n">
+        <v>249.48</v>
+      </c>
+      <c r="L15" s="8" t="inlineStr"/>
+      <c r="M15" s="8" t="inlineStr"/>
+      <c r="N15" s="8" t="inlineStr"/>
+      <c r="O15" s="8" t="inlineStr"/>
+      <c r="P15" s="9" t="inlineStr"/>
+      <c r="Q15" s="7" t="inlineStr"/>
+      <c r="R15" s="7" t="inlineStr"/>
+      <c r="S15" s="7" t="inlineStr"/>
+      <c r="T15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="7" t="inlineStr">
+        <is>
+          <t>29/07/2026 06:07 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>553.45</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="n">
+        <v>520.91</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>553.45</v>
+      </c>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="6" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>29/07/2026 06:07 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>4422.7</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>142.8</v>
+      </c>
+      <c r="H17" s="7" t="inlineStr"/>
+      <c r="I17" s="8" t="inlineStr"/>
+      <c r="J17" s="8" t="n">
+        <v>3994.3</v>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>4422.7</v>
+      </c>
+      <c r="L17" s="8" t="inlineStr"/>
+      <c r="M17" s="8" t="inlineStr"/>
+      <c r="N17" s="8" t="inlineStr"/>
+      <c r="O17" s="8" t="inlineStr"/>
+      <c r="P17" s="9" t="inlineStr"/>
+      <c r="Q17" s="7" t="inlineStr"/>
+      <c r="R17" s="7" t="inlineStr"/>
+      <c r="S17" s="7" t="inlineStr"/>
+      <c r="T17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="7" t="inlineStr">
+        <is>
+          <t>29/07/2026 06:07 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3931.4</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>65.56</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="n">
+        <v>3734.73</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>3931.4</v>
+      </c>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="6" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr"/>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>29/07/2026 06:07 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>NSLNISP</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>43.06</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H19" s="7" t="inlineStr"/>
+      <c r="I19" s="8" t="inlineStr"/>
+      <c r="J19" s="8" t="n">
+        <v>40.18</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>43.06</v>
+      </c>
+      <c r="L19" s="8" t="inlineStr"/>
+      <c r="M19" s="8" t="inlineStr"/>
+      <c r="N19" s="8" t="inlineStr"/>
+      <c r="O19" s="8" t="inlineStr"/>
+      <c r="P19" s="9" t="inlineStr"/>
+      <c r="Q19" s="7" t="inlineStr"/>
+      <c r="R19" s="7" t="inlineStr"/>
+      <c r="S19" s="7" t="inlineStr"/>
+      <c r="T19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="7" t="inlineStr">
+        <is>
+          <t>29/07/2026 06:07 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>PFOCUS</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>308.72</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="n">
+        <v>266.87</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>308.72</v>
+      </c>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="6" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr"/>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>29/07/2026 06:07 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>1894.9</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>38.19</v>
+      </c>
+      <c r="H21" s="7" t="inlineStr"/>
+      <c r="I21" s="8" t="inlineStr"/>
+      <c r="J21" s="8" t="n">
+        <v>1780.34</v>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>1894.9</v>
+      </c>
+      <c r="L21" s="8" t="inlineStr"/>
+      <c r="M21" s="8" t="inlineStr"/>
+      <c r="N21" s="8" t="inlineStr"/>
+      <c r="O21" s="8" t="inlineStr"/>
+      <c r="P21" s="9" t="inlineStr"/>
+      <c r="Q21" s="7" t="inlineStr"/>
+      <c r="R21" s="7" t="inlineStr"/>
+      <c r="S21" s="7" t="inlineStr"/>
+      <c r="T21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="7" t="inlineStr">
+        <is>
+          <t>29/07/2026 06:07 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>TATAINVEST</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>675.75</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="n">
+        <v>631.42</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>675.75</v>
+      </c>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="6" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr"/>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>29/07/2026 06:07 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:U1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/portfolio_tracker.xlsx
+++ b/portfolio_tracker.xlsx
@@ -185,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -256,6 +256,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -644,7 +647,7 @@
     <row r="3">
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Last updated: 29 Jul 2026, 06:07 PM IST</t>
+          <t>Last updated: 30 Jul 2026, 05:48 PM IST</t>
         </is>
       </c>
     </row>
@@ -667,10 +670,10 @@
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="B6" s="15" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F6" s="17" t="n">
         <v>0</v>
@@ -1107,7 +1110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U22"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1282,32 +1285,32 @@
         <v>479.1</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>525.8499755859375</v>
+        <v>525.1500244140625</v>
       </c>
       <c r="L2" s="5" t="n">
         <v>525.8499755859375</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>480.11</v>
+        <v>481.34</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>485.4</v>
+        <v>487.78</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>0.85</v>
+        <v>0.15</v>
       </c>
       <c r="P2" s="25" t="n">
-        <v>0.0016</v>
+        <v>0.0003</v>
       </c>
       <c r="Q2" s="3" t="inlineStr"/>
       <c r="R2" s="3" t="inlineStr"/>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026 06:03 PM IST</t>
+          <t>30/07/2026 05:45 PM IST</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1356,7 @@
         <v>121.23</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>134.1900024414062</v>
+        <v>131.3999938964844</v>
       </c>
       <c r="L3" s="8" t="n">
         <v>134.1900024414062</v>
@@ -1362,23 +1365,23 @@
         <v>122.26</v>
       </c>
       <c r="N3" s="8" t="n">
-        <v>123.15</v>
+        <v>123.55</v>
       </c>
       <c r="O3" s="8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P3" s="25" t="n">
-        <v>0.009299999999999999</v>
+        <v>-1.56</v>
+      </c>
+      <c r="P3" s="26" t="n">
+        <v>-0.0117</v>
       </c>
       <c r="Q3" s="7" t="inlineStr"/>
       <c r="R3" s="7" t="inlineStr"/>
       <c r="S3" s="7" t="inlineStr"/>
       <c r="T3" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" s="7" t="inlineStr">
         <is>
-          <t>29/07/2026 06:03 PM IST</t>
+          <t>30/07/2026 05:45 PM IST</t>
         </is>
       </c>
     </row>
@@ -1424,32 +1427,32 @@
         <v>4436.59</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4755.10009765625</v>
+        <v>4801.2998046875</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>4755.10009765625</v>
+        <v>4801.2998046875</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>4454.29</v>
+        <v>4516.04</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>4589.38</v>
+        <v>4611.02</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>20.1</v>
+        <v>66.3</v>
       </c>
       <c r="P4" s="25" t="n">
-        <v>0.0042</v>
+        <v>0.014</v>
       </c>
       <c r="Q4" s="3" t="inlineStr"/>
       <c r="R4" s="3" t="inlineStr"/>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026 06:03 PM IST</t>
+          <t>30/07/2026 05:45 PM IST</t>
         </is>
       </c>
     </row>
@@ -1472,9 +1475,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>PENDING ENTRY</t>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F5" s="8" t="n">
@@ -1483,19 +1486,33 @@
       <c r="G5" s="7" t="n">
         <v>10.89</v>
       </c>
-      <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>285.99</v>
+      </c>
       <c r="J5" s="8" t="n">
-        <v>235.8</v>
+        <v>253.32</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>268.47</v>
-      </c>
-      <c r="L5" s="8" t="inlineStr"/>
-      <c r="M5" s="8" t="inlineStr"/>
+        <v>285.99</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>285.99</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>253.32</v>
+      </c>
       <c r="N5" s="8" t="inlineStr"/>
-      <c r="O5" s="8" t="inlineStr"/>
-      <c r="P5" s="9" t="inlineStr"/>
+      <c r="O5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q5" s="7" t="inlineStr"/>
       <c r="R5" s="7" t="inlineStr"/>
       <c r="S5" s="7" t="inlineStr"/>
@@ -1504,7 +1521,7 @@
       </c>
       <c r="U5" s="7" t="inlineStr">
         <is>
-          <t>29/07/2026 09:08 AM IST</t>
+          <t>30/07/2026 05:45 PM IST</t>
         </is>
       </c>
     </row>
@@ -1527,9 +1544,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>PENDING ENTRY</t>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
@@ -1538,19 +1555,33 @@
       <c r="G6" s="3" t="n">
         <v>10.99</v>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>434.5</v>
+      </c>
       <c r="J6" s="5" t="n">
-        <v>402.34</v>
+        <v>401.53</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>435.3</v>
-      </c>
-      <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr"/>
+        <v>434.5</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>434.5</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>401.53</v>
+      </c>
       <c r="N6" s="5" t="inlineStr"/>
-      <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="6" t="inlineStr"/>
+      <c r="O6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q6" s="3" t="inlineStr"/>
       <c r="R6" s="3" t="inlineStr"/>
       <c r="S6" s="3" t="inlineStr"/>
@@ -1559,7 +1590,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026 06:07 PM IST</t>
+          <t>30/07/2026 05:45 PM IST</t>
         </is>
       </c>
     </row>
@@ -1582,9 +1613,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>PENDING ENTRY</t>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F7" s="8" t="n">
@@ -1593,19 +1624,33 @@
       <c r="G7" s="7" t="n">
         <v>1.37</v>
       </c>
-      <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="8" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>87.53</v>
+      </c>
       <c r="J7" s="8" t="n">
-        <v>83.52</v>
+        <v>83.42</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>87.63</v>
-      </c>
-      <c r="L7" s="8" t="inlineStr"/>
-      <c r="M7" s="8" t="inlineStr"/>
+        <v>87.53</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>87.53</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>83.42</v>
+      </c>
       <c r="N7" s="8" t="inlineStr"/>
-      <c r="O7" s="8" t="inlineStr"/>
-      <c r="P7" s="9" t="inlineStr"/>
+      <c r="O7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q7" s="7" t="inlineStr"/>
       <c r="R7" s="7" t="inlineStr"/>
       <c r="S7" s="7" t="inlineStr"/>
@@ -1614,7 +1659,7 @@
       </c>
       <c r="U7" s="7" t="inlineStr">
         <is>
-          <t>29/07/2026 06:07 PM IST</t>
+          <t>30/07/2026 05:45 PM IST</t>
         </is>
       </c>
     </row>
@@ -1637,9 +1682,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>PENDING ENTRY</t>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
@@ -1648,19 +1693,33 @@
       <c r="G8" s="3" t="n">
         <v>99.75</v>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>5528</v>
+      </c>
       <c r="J8" s="5" t="n">
-        <v>5218.25</v>
+        <v>5228.75</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>5517.5</v>
-      </c>
-      <c r="L8" s="5" t="inlineStr"/>
-      <c r="M8" s="5" t="inlineStr"/>
+        <v>5528</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>5528</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>5228.75</v>
+      </c>
       <c r="N8" s="5" t="inlineStr"/>
-      <c r="O8" s="5" t="inlineStr"/>
-      <c r="P8" s="6" t="inlineStr"/>
+      <c r="O8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q8" s="3" t="inlineStr"/>
       <c r="R8" s="3" t="inlineStr"/>
       <c r="S8" s="3" t="inlineStr"/>
@@ -1669,7 +1728,7 @@
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026 06:07 PM IST</t>
+          <t>30/07/2026 05:45 PM IST</t>
         </is>
       </c>
     </row>
@@ -1692,9 +1751,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>PENDING ENTRY</t>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F9" s="8" t="n">
@@ -1703,19 +1762,33 @@
       <c r="G9" s="7" t="n">
         <v>7.06</v>
       </c>
-      <c r="H9" s="7" t="inlineStr"/>
-      <c r="I9" s="8" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>264.2</v>
+      </c>
       <c r="J9" s="8" t="n">
-        <v>243.07</v>
+        <v>243.02</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>264.25</v>
-      </c>
-      <c r="L9" s="8" t="inlineStr"/>
-      <c r="M9" s="8" t="inlineStr"/>
+        <v>264.2</v>
+      </c>
+      <c r="L9" s="8" t="n">
+        <v>264.2</v>
+      </c>
+      <c r="M9" s="8" t="n">
+        <v>243.02</v>
+      </c>
       <c r="N9" s="8" t="inlineStr"/>
-      <c r="O9" s="8" t="inlineStr"/>
-      <c r="P9" s="9" t="inlineStr"/>
+      <c r="O9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q9" s="7" t="inlineStr"/>
       <c r="R9" s="7" t="inlineStr"/>
       <c r="S9" s="7" t="inlineStr"/>
@@ -1724,7 +1797,7 @@
       </c>
       <c r="U9" s="7" t="inlineStr">
         <is>
-          <t>29/07/2026 06:07 PM IST</t>
+          <t>30/07/2026 05:45 PM IST</t>
         </is>
       </c>
     </row>
@@ -1747,9 +1820,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>PENDING ENTRY</t>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
@@ -1758,19 +1831,33 @@
       <c r="G10" s="3" t="n">
         <v>55.59</v>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>2265.5</v>
+      </c>
       <c r="J10" s="5" t="n">
-        <v>2113.64</v>
+        <v>2098.73</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>2280.4</v>
-      </c>
-      <c r="L10" s="5" t="inlineStr"/>
-      <c r="M10" s="5" t="inlineStr"/>
+        <v>2265.5</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>2265.5</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>2098.73</v>
+      </c>
       <c r="N10" s="5" t="inlineStr"/>
-      <c r="O10" s="5" t="inlineStr"/>
-      <c r="P10" s="6" t="inlineStr"/>
+      <c r="O10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q10" s="3" t="inlineStr"/>
       <c r="R10" s="3" t="inlineStr"/>
       <c r="S10" s="3" t="inlineStr"/>
@@ -1779,7 +1866,7 @@
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026 06:07 PM IST</t>
+          <t>30/07/2026 05:45 PM IST</t>
         </is>
       </c>
     </row>
@@ -1802,9 +1889,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>PENDING ENTRY</t>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F11" s="8" t="n">
@@ -1813,19 +1900,33 @@
       <c r="G11" s="7" t="n">
         <v>3.58</v>
       </c>
-      <c r="H11" s="7" t="inlineStr"/>
-      <c r="I11" s="8" t="inlineStr"/>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>119.06</v>
+      </c>
       <c r="J11" s="8" t="n">
-        <v>107.63</v>
+        <v>108.32</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>118.36</v>
-      </c>
-      <c r="L11" s="8" t="inlineStr"/>
-      <c r="M11" s="8" t="inlineStr"/>
+        <v>119.06</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>119.06</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>108.32</v>
+      </c>
       <c r="N11" s="8" t="inlineStr"/>
-      <c r="O11" s="8" t="inlineStr"/>
-      <c r="P11" s="9" t="inlineStr"/>
+      <c r="O11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q11" s="7" t="inlineStr"/>
       <c r="R11" s="7" t="inlineStr"/>
       <c r="S11" s="7" t="inlineStr"/>
@@ -1834,7 +1935,7 @@
       </c>
       <c r="U11" s="7" t="inlineStr">
         <is>
-          <t>29/07/2026 06:07 PM IST</t>
+          <t>30/07/2026 05:45 PM IST</t>
         </is>
       </c>
     </row>
@@ -1857,9 +1958,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>PENDING ENTRY</t>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
@@ -1868,19 +1969,33 @@
       <c r="G12" s="3" t="n">
         <v>59.31</v>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>3016.8</v>
+      </c>
       <c r="J12" s="5" t="n">
-        <v>2838.88</v>
+        <v>2838.87</v>
       </c>
       <c r="K12" s="5" t="n">
         <v>3016.8</v>
       </c>
-      <c r="L12" s="5" t="inlineStr"/>
-      <c r="M12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="n">
+        <v>3016.8</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>2838.87</v>
+      </c>
       <c r="N12" s="5" t="inlineStr"/>
-      <c r="O12" s="5" t="inlineStr"/>
-      <c r="P12" s="6" t="inlineStr"/>
+      <c r="O12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q12" s="3" t="inlineStr"/>
       <c r="R12" s="3" t="inlineStr"/>
       <c r="S12" s="3" t="inlineStr"/>
@@ -1889,7 +2004,7 @@
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026 06:07 PM IST</t>
+          <t>30/07/2026 05:45 PM IST</t>
         </is>
       </c>
     </row>
@@ -1912,9 +2027,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>PENDING ENTRY</t>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F13" s="8" t="n">
@@ -1923,19 +2038,33 @@
       <c r="G13" s="7" t="n">
         <v>49.88</v>
       </c>
-      <c r="H13" s="7" t="inlineStr"/>
-      <c r="I13" s="8" t="inlineStr"/>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>2270.2</v>
+      </c>
       <c r="J13" s="8" t="n">
-        <v>2112.06</v>
+        <v>2120.56</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>2261.7</v>
-      </c>
-      <c r="L13" s="8" t="inlineStr"/>
-      <c r="M13" s="8" t="inlineStr"/>
+        <v>2270.2</v>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>2270.2</v>
+      </c>
+      <c r="M13" s="8" t="n">
+        <v>2120.56</v>
+      </c>
       <c r="N13" s="8" t="inlineStr"/>
-      <c r="O13" s="8" t="inlineStr"/>
-      <c r="P13" s="9" t="inlineStr"/>
+      <c r="O13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q13" s="7" t="inlineStr"/>
       <c r="R13" s="7" t="inlineStr"/>
       <c r="S13" s="7" t="inlineStr"/>
@@ -1944,7 +2073,7 @@
       </c>
       <c r="U13" s="7" t="inlineStr">
         <is>
-          <t>29/07/2026 06:07 PM IST</t>
+          <t>30/07/2026 05:45 PM IST</t>
         </is>
       </c>
     </row>
@@ -1967,9 +2096,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>PENDING ENTRY</t>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
@@ -1978,19 +2107,33 @@
       <c r="G14" s="3" t="n">
         <v>99.55</v>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>5168.8</v>
+      </c>
       <c r="J14" s="5" t="n">
-        <v>4850.44</v>
+        <v>4870.15</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>5149.1</v>
-      </c>
-      <c r="L14" s="5" t="inlineStr"/>
-      <c r="M14" s="5" t="inlineStr"/>
+        <v>5168.8</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>5168.8</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>4870.15</v>
+      </c>
       <c r="N14" s="5" t="inlineStr"/>
-      <c r="O14" s="5" t="inlineStr"/>
-      <c r="P14" s="6" t="inlineStr"/>
+      <c r="O14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q14" s="3" t="inlineStr"/>
       <c r="R14" s="3" t="inlineStr"/>
       <c r="S14" s="3" t="inlineStr"/>
@@ -1999,7 +2142,7 @@
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026 06:07 PM IST</t>
+          <t>30/07/2026 05:45 PM IST</t>
         </is>
       </c>
     </row>
@@ -2022,9 +2165,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>PENDING ENTRY</t>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F15" s="8" t="n">
@@ -2033,19 +2176,33 @@
       <c r="G15" s="7" t="n">
         <v>6.38</v>
       </c>
-      <c r="H15" s="7" t="inlineStr"/>
-      <c r="I15" s="8" t="inlineStr"/>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="n">
+        <v>248.75</v>
+      </c>
       <c r="J15" s="8" t="n">
-        <v>230.33</v>
+        <v>229.61</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>249.48</v>
-      </c>
-      <c r="L15" s="8" t="inlineStr"/>
-      <c r="M15" s="8" t="inlineStr"/>
+        <v>248.75</v>
+      </c>
+      <c r="L15" s="8" t="n">
+        <v>248.75</v>
+      </c>
+      <c r="M15" s="8" t="n">
+        <v>229.61</v>
+      </c>
       <c r="N15" s="8" t="inlineStr"/>
-      <c r="O15" s="8" t="inlineStr"/>
-      <c r="P15" s="9" t="inlineStr"/>
+      <c r="O15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q15" s="7" t="inlineStr"/>
       <c r="R15" s="7" t="inlineStr"/>
       <c r="S15" s="7" t="inlineStr"/>
@@ -2054,7 +2211,7 @@
       </c>
       <c r="U15" s="7" t="inlineStr">
         <is>
-          <t>29/07/2026 06:07 PM IST</t>
+          <t>30/07/2026 05:45 PM IST</t>
         </is>
       </c>
     </row>
@@ -2077,9 +2234,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>PENDING ENTRY</t>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
@@ -2088,19 +2245,33 @@
       <c r="G16" s="3" t="n">
         <v>10.85</v>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>553.4</v>
+      </c>
       <c r="J16" s="5" t="n">
-        <v>520.91</v>
+        <v>520.85</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>553.45</v>
-      </c>
-      <c r="L16" s="5" t="inlineStr"/>
-      <c r="M16" s="5" t="inlineStr"/>
+        <v>553.4</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>553.4</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>520.85</v>
+      </c>
       <c r="N16" s="5" t="inlineStr"/>
-      <c r="O16" s="5" t="inlineStr"/>
-      <c r="P16" s="6" t="inlineStr"/>
+      <c r="O16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q16" s="3" t="inlineStr"/>
       <c r="R16" s="3" t="inlineStr"/>
       <c r="S16" s="3" t="inlineStr"/>
@@ -2109,7 +2280,7 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026 06:07 PM IST</t>
+          <t>30/07/2026 05:45 PM IST</t>
         </is>
       </c>
     </row>
@@ -2132,9 +2303,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>PENDING ENTRY</t>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F17" s="8" t="n">
@@ -2143,19 +2314,33 @@
       <c r="G17" s="7" t="n">
         <v>142.8</v>
       </c>
-      <c r="H17" s="7" t="inlineStr"/>
-      <c r="I17" s="8" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>4422.8</v>
+      </c>
       <c r="J17" s="8" t="n">
-        <v>3994.3</v>
+        <v>3994.4</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>4422.7</v>
-      </c>
-      <c r="L17" s="8" t="inlineStr"/>
-      <c r="M17" s="8" t="inlineStr"/>
+        <v>4422.8</v>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>4422.8</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>3994.4</v>
+      </c>
       <c r="N17" s="8" t="inlineStr"/>
-      <c r="O17" s="8" t="inlineStr"/>
-      <c r="P17" s="9" t="inlineStr"/>
+      <c r="O17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q17" s="7" t="inlineStr"/>
       <c r="R17" s="7" t="inlineStr"/>
       <c r="S17" s="7" t="inlineStr"/>
@@ -2164,7 +2349,7 @@
       </c>
       <c r="U17" s="7" t="inlineStr">
         <is>
-          <t>29/07/2026 06:07 PM IST</t>
+          <t>30/07/2026 05:45 PM IST</t>
         </is>
       </c>
     </row>
@@ -2187,9 +2372,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>PENDING ENTRY</t>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
@@ -2198,19 +2383,33 @@
       <c r="G18" s="3" t="n">
         <v>65.56</v>
       </c>
-      <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>3931.4</v>
+      </c>
       <c r="J18" s="5" t="n">
-        <v>3734.73</v>
+        <v>3734.72</v>
       </c>
       <c r="K18" s="5" t="n">
         <v>3931.4</v>
       </c>
-      <c r="L18" s="5" t="inlineStr"/>
-      <c r="M18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="n">
+        <v>3931.4</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>3734.72</v>
+      </c>
       <c r="N18" s="5" t="inlineStr"/>
-      <c r="O18" s="5" t="inlineStr"/>
-      <c r="P18" s="6" t="inlineStr"/>
+      <c r="O18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q18" s="3" t="inlineStr"/>
       <c r="R18" s="3" t="inlineStr"/>
       <c r="S18" s="3" t="inlineStr"/>
@@ -2219,7 +2418,7 @@
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026 06:07 PM IST</t>
+          <t>30/07/2026 05:45 PM IST</t>
         </is>
       </c>
     </row>
@@ -2242,9 +2441,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>PENDING ENTRY</t>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F19" s="8" t="n">
@@ -2253,19 +2452,33 @@
       <c r="G19" s="7" t="n">
         <v>0.96</v>
       </c>
-      <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="8" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>43</v>
+      </c>
       <c r="J19" s="8" t="n">
-        <v>40.18</v>
+        <v>40.12</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>43.06</v>
-      </c>
-      <c r="L19" s="8" t="inlineStr"/>
-      <c r="M19" s="8" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>40.12</v>
+      </c>
       <c r="N19" s="8" t="inlineStr"/>
-      <c r="O19" s="8" t="inlineStr"/>
-      <c r="P19" s="9" t="inlineStr"/>
+      <c r="O19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q19" s="7" t="inlineStr"/>
       <c r="R19" s="7" t="inlineStr"/>
       <c r="S19" s="7" t="inlineStr"/>
@@ -2274,7 +2487,7 @@
       </c>
       <c r="U19" s="7" t="inlineStr">
         <is>
-          <t>29/07/2026 06:07 PM IST</t>
+          <t>30/07/2026 05:45 PM IST</t>
         </is>
       </c>
     </row>
@@ -2297,9 +2510,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>PENDING ENTRY</t>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
@@ -2308,19 +2521,33 @@
       <c r="G20" s="3" t="n">
         <v>13.95</v>
       </c>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="5" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>304.15</v>
+      </c>
       <c r="J20" s="5" t="n">
-        <v>266.87</v>
+        <v>262.3</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>308.72</v>
-      </c>
-      <c r="L20" s="5" t="inlineStr"/>
-      <c r="M20" s="5" t="inlineStr"/>
+        <v>304.15</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>304.15</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>262.3</v>
+      </c>
       <c r="N20" s="5" t="inlineStr"/>
-      <c r="O20" s="5" t="inlineStr"/>
-      <c r="P20" s="6" t="inlineStr"/>
+      <c r="O20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q20" s="3" t="inlineStr"/>
       <c r="R20" s="3" t="inlineStr"/>
       <c r="S20" s="3" t="inlineStr"/>
@@ -2329,7 +2556,7 @@
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026 06:07 PM IST</t>
+          <t>30/07/2026 05:45 PM IST</t>
         </is>
       </c>
     </row>
@@ -2352,9 +2579,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>PENDING ENTRY</t>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F21" s="8" t="n">
@@ -2363,19 +2590,33 @@
       <c r="G21" s="7" t="n">
         <v>38.19</v>
       </c>
-      <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="8" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>1882.2</v>
+      </c>
       <c r="J21" s="8" t="n">
-        <v>1780.34</v>
+        <v>1767.63</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>1894.9</v>
-      </c>
-      <c r="L21" s="8" t="inlineStr"/>
-      <c r="M21" s="8" t="inlineStr"/>
+        <v>1882.2</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>1882.2</v>
+      </c>
+      <c r="M21" s="8" t="n">
+        <v>1767.63</v>
+      </c>
       <c r="N21" s="8" t="inlineStr"/>
-      <c r="O21" s="8" t="inlineStr"/>
-      <c r="P21" s="9" t="inlineStr"/>
+      <c r="O21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q21" s="7" t="inlineStr"/>
       <c r="R21" s="7" t="inlineStr"/>
       <c r="S21" s="7" t="inlineStr"/>
@@ -2384,7 +2625,7 @@
       </c>
       <c r="U21" s="7" t="inlineStr">
         <is>
-          <t>29/07/2026 06:07 PM IST</t>
+          <t>30/07/2026 05:45 PM IST</t>
         </is>
       </c>
     </row>
@@ -2407,9 +2648,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>PENDING ENTRY</t>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
@@ -2418,19 +2659,33 @@
       <c r="G22" s="3" t="n">
         <v>14.78</v>
       </c>
-      <c r="H22" s="3" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>678</v>
+      </c>
       <c r="J22" s="5" t="n">
-        <v>631.42</v>
+        <v>633.66</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>675.75</v>
-      </c>
-      <c r="L22" s="5" t="inlineStr"/>
-      <c r="M22" s="5" t="inlineStr"/>
+        <v>678</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>678</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>633.66</v>
+      </c>
       <c r="N22" s="5" t="inlineStr"/>
-      <c r="O22" s="5" t="inlineStr"/>
-      <c r="P22" s="6" t="inlineStr"/>
+      <c r="O22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q22" s="3" t="inlineStr"/>
       <c r="R22" s="3" t="inlineStr"/>
       <c r="S22" s="3" t="inlineStr"/>
@@ -2439,7 +2694,172 @@
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026 06:07 PM IST</t>
+          <t>30/07/2026 05:45 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>1261.7</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>28.41</v>
+      </c>
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="8" t="inlineStr"/>
+      <c r="J23" s="8" t="n">
+        <v>1176.46</v>
+      </c>
+      <c r="K23" s="8" t="n">
+        <v>1261.7</v>
+      </c>
+      <c r="L23" s="8" t="inlineStr"/>
+      <c r="M23" s="8" t="inlineStr"/>
+      <c r="N23" s="8" t="inlineStr"/>
+      <c r="O23" s="8" t="inlineStr"/>
+      <c r="P23" s="9" t="inlineStr"/>
+      <c r="Q23" s="7" t="inlineStr"/>
+      <c r="R23" s="7" t="inlineStr"/>
+      <c r="S23" s="7" t="inlineStr"/>
+      <c r="T23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="7" t="inlineStr">
+        <is>
+          <t>30/07/2026 05:48 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>MRPL</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>166.84</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="n">
+        <v>138.96</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>166.84</v>
+      </c>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="6" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr"/>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>30/07/2026 05:48 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>TMCV</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>414.95</v>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="H25" s="7" t="inlineStr"/>
+      <c r="I25" s="8" t="inlineStr"/>
+      <c r="J25" s="8" t="n">
+        <v>385.06</v>
+      </c>
+      <c r="K25" s="8" t="n">
+        <v>414.95</v>
+      </c>
+      <c r="L25" s="8" t="inlineStr"/>
+      <c r="M25" s="8" t="inlineStr"/>
+      <c r="N25" s="8" t="inlineStr"/>
+      <c r="O25" s="8" t="inlineStr"/>
+      <c r="P25" s="9" t="inlineStr"/>
+      <c r="Q25" s="7" t="inlineStr"/>
+      <c r="R25" s="7" t="inlineStr"/>
+      <c r="S25" s="7" t="inlineStr"/>
+      <c r="T25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="7" t="inlineStr">
+        <is>
+          <t>30/07/2026 05:48 PM IST</t>
         </is>
       </c>
     </row>

--- a/portfolio_tracker.xlsx
+++ b/portfolio_tracker.xlsx
@@ -185,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -259,6 +259,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -647,7 +650,7 @@
     <row r="3">
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Last updated: 30 Jul 2026, 05:48 PM IST</t>
+          <t>Last updated: 31 Jul 2026, 06:05 PM IST</t>
         </is>
       </c>
     </row>
@@ -670,13 +673,13 @@
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="B6" s="15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F6" s="17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -685,7 +688,7 @@
           <t>WIN RATE</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>AVG P&amp;L (EXITED)</t>
         </is>
@@ -702,14 +705,14 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>-1.92%</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.24%</t>
         </is>
       </c>
     </row>
@@ -723,7 +726,7 @@
     <row r="12" ht="32" customHeight="1">
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-5.48%</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U25"/>
+  <dimension ref="A1:U34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1285,32 +1288,32 @@
         <v>479.1</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>525.1500244140625</v>
+        <v>525.5</v>
       </c>
       <c r="L2" s="5" t="n">
         <v>525.8499755859375</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>481.34</v>
+        <v>482.65</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>487.78</v>
+        <v>489.65</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="P2" s="25" t="n">
-        <v>0.0003</v>
+        <v>0.001</v>
       </c>
       <c r="Q2" s="3" t="inlineStr"/>
       <c r="R2" s="3" t="inlineStr"/>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026 05:45 PM IST</t>
+          <t>31/07/2026 06:01 PM IST</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1359,7 @@
         <v>121.23</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>131.3999938964844</v>
+        <v>132.2400054931641</v>
       </c>
       <c r="L3" s="8" t="n">
         <v>134.1900024414062</v>
@@ -1365,23 +1368,23 @@
         <v>122.26</v>
       </c>
       <c r="N3" s="8" t="n">
-        <v>123.55</v>
+        <v>123.96</v>
       </c>
       <c r="O3" s="8" t="n">
-        <v>-1.56</v>
+        <v>-0.72</v>
       </c>
       <c r="P3" s="26" t="n">
-        <v>-0.0117</v>
+        <v>-0.0054</v>
       </c>
       <c r="Q3" s="7" t="inlineStr"/>
       <c r="R3" s="7" t="inlineStr"/>
       <c r="S3" s="7" t="inlineStr"/>
       <c r="T3" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U3" s="7" t="inlineStr">
         <is>
-          <t>30/07/2026 05:45 PM IST</t>
+          <t>31/07/2026 06:01 PM IST</t>
         </is>
       </c>
     </row>
@@ -1427,32 +1430,32 @@
         <v>4436.59</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4801.2998046875</v>
+        <v>4823.89990234375</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>4801.2998046875</v>
+        <v>4823.89990234375</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>4516.04</v>
+        <v>4534.78</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>4611.02</v>
+        <v>4627.43</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>66.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P4" s="25" t="n">
-        <v>0.014</v>
+        <v>0.0188</v>
       </c>
       <c r="Q4" s="3" t="inlineStr"/>
       <c r="R4" s="3" t="inlineStr"/>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026 05:45 PM IST</t>
+          <t>31/07/2026 06:01 PM IST</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1501,7 @@
         <v>253.32</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>285.99</v>
+        <v>284.8599853515625</v>
       </c>
       <c r="L5" s="8" t="n">
         <v>285.99</v>
@@ -1506,22 +1509,24 @@
       <c r="M5" s="8" t="n">
         <v>253.32</v>
       </c>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="n">
+        <v>269.39</v>
+      </c>
       <c r="O5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="25" t="n">
-        <v>0</v>
+        <v>-1.13</v>
+      </c>
+      <c r="P5" s="26" t="n">
+        <v>-0.004</v>
       </c>
       <c r="Q5" s="7" t="inlineStr"/>
       <c r="R5" s="7" t="inlineStr"/>
       <c r="S5" s="7" t="inlineStr"/>
       <c r="T5" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" s="7" t="inlineStr">
         <is>
-          <t>30/07/2026 05:45 PM IST</t>
+          <t>31/07/2026 06:01 PM IST</t>
         </is>
       </c>
     </row>
@@ -1544,9 +1549,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="E6" s="27" t="inlineStr">
+        <is>
+          <t>EXITED</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
@@ -1567,30 +1572,42 @@
         <v>401.53</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>434.5</v>
+        <v>432.2</v>
       </c>
       <c r="L6" s="5" t="n">
         <v>434.5</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>401.53</v>
-      </c>
-      <c r="N6" s="5" t="inlineStr"/>
+        <v>401.99</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>432.45</v>
+      </c>
       <c r="O6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
+        <v>-2.3</v>
+      </c>
+      <c r="P6" s="26" t="n">
+        <v>-0.0053</v>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>432.2</v>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>Price crossed below 20 SMA</t>
+        </is>
+      </c>
       <c r="T6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026 05:45 PM IST</t>
+          <t>31/07/2026 06:01 PM IST</t>
         </is>
       </c>
     </row>
@@ -1613,9 +1630,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E7" s="24" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>EXITED</t>
         </is>
       </c>
       <c r="F7" s="8" t="n">
@@ -1636,7 +1653,7 @@
         <v>83.42</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>87.53</v>
+        <v>86.02</v>
       </c>
       <c r="L7" s="8" t="n">
         <v>87.53</v>
@@ -1644,22 +1661,34 @@
       <c r="M7" s="8" t="n">
         <v>83.42</v>
       </c>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="8" t="n">
+        <v>86.72</v>
+      </c>
       <c r="O7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="7" t="inlineStr"/>
-      <c r="R7" s="7" t="inlineStr"/>
-      <c r="S7" s="7" t="inlineStr"/>
+        <v>-1.51</v>
+      </c>
+      <c r="P7" s="26" t="n">
+        <v>-0.0173</v>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="R7" s="7" t="n">
+        <v>86.02</v>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>Price crossed below 20 SMA</t>
+        </is>
+      </c>
       <c r="T7" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" s="7" t="inlineStr">
         <is>
-          <t>30/07/2026 05:45 PM IST</t>
+          <t>31/07/2026 06:01 PM IST</t>
         </is>
       </c>
     </row>
@@ -1705,30 +1734,32 @@
         <v>5228.75</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>5528</v>
+        <v>5416.5</v>
       </c>
       <c r="L8" s="5" t="n">
         <v>5528</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>5228.75</v>
-      </c>
-      <c r="N8" s="5" t="inlineStr"/>
+        <v>5230.05</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>5322.3</v>
+      </c>
       <c r="O8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="25" t="n">
-        <v>0</v>
+        <v>-111.5</v>
+      </c>
+      <c r="P8" s="26" t="n">
+        <v>-0.0202</v>
       </c>
       <c r="Q8" s="3" t="inlineStr"/>
       <c r="R8" s="3" t="inlineStr"/>
       <c r="S8" s="3" t="inlineStr"/>
       <c r="T8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026 05:45 PM IST</t>
+          <t>31/07/2026 06:01 PM IST</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1805,7 @@
         <v>243.02</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>264.2</v>
+        <v>260.2000122070312</v>
       </c>
       <c r="L9" s="8" t="n">
         <v>264.2</v>
@@ -1782,22 +1813,24 @@
       <c r="M9" s="8" t="n">
         <v>243.02</v>
       </c>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="8" t="n">
+        <v>256.81</v>
+      </c>
       <c r="O9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="25" t="n">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="P9" s="26" t="n">
+        <v>-0.0151</v>
       </c>
       <c r="Q9" s="7" t="inlineStr"/>
       <c r="R9" s="7" t="inlineStr"/>
       <c r="S9" s="7" t="inlineStr"/>
       <c r="T9" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" s="7" t="inlineStr">
         <is>
-          <t>30/07/2026 05:45 PM IST</t>
+          <t>31/07/2026 06:01 PM IST</t>
         </is>
       </c>
     </row>
@@ -1820,9 +1853,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E10" s="24" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="E10" s="27" t="inlineStr">
+        <is>
+          <t>EXITED</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
@@ -1843,30 +1876,42 @@
         <v>2098.73</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>2265.5</v>
+        <v>2260</v>
       </c>
       <c r="L10" s="5" t="n">
         <v>2265.5</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>2098.73</v>
-      </c>
-      <c r="N10" s="5" t="inlineStr"/>
+        <v>2110.14</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>2282.05</v>
+      </c>
       <c r="O10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr"/>
+        <v>-5.5</v>
+      </c>
+      <c r="P10" s="26" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>2260</v>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t>Price crossed below 20 SMA</t>
+        </is>
+      </c>
       <c r="T10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026 05:45 PM IST</t>
+          <t>31/07/2026 06:01 PM IST</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1957,7 @@
         <v>108.32</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>119.06</v>
+        <v>114.1800003051758</v>
       </c>
       <c r="L11" s="8" t="n">
         <v>119.06</v>
@@ -1920,22 +1965,24 @@
       <c r="M11" s="8" t="n">
         <v>108.32</v>
       </c>
-      <c r="N11" s="8" t="inlineStr"/>
+      <c r="N11" s="8" t="n">
+        <v>113.08</v>
+      </c>
       <c r="O11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="25" t="n">
-        <v>0</v>
+        <v>-4.88</v>
+      </c>
+      <c r="P11" s="26" t="n">
+        <v>-0.041</v>
       </c>
       <c r="Q11" s="7" t="inlineStr"/>
       <c r="R11" s="7" t="inlineStr"/>
       <c r="S11" s="7" t="inlineStr"/>
       <c r="T11" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" s="7" t="inlineStr">
         <is>
-          <t>30/07/2026 05:45 PM IST</t>
+          <t>31/07/2026 06:01 PM IST</t>
         </is>
       </c>
     </row>
@@ -1981,30 +2028,32 @@
         <v>2838.87</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>3016.8</v>
+        <v>3086</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>3016.8</v>
+        <v>3086</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>2838.87</v>
-      </c>
-      <c r="N12" s="5" t="inlineStr"/>
+        <v>2908.29</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>2960.46</v>
+      </c>
       <c r="O12" s="5" t="n">
-        <v>0</v>
+        <v>69.2</v>
       </c>
       <c r="P12" s="25" t="n">
-        <v>0</v>
+        <v>0.0229</v>
       </c>
       <c r="Q12" s="3" t="inlineStr"/>
       <c r="R12" s="3" t="inlineStr"/>
       <c r="S12" s="3" t="inlineStr"/>
       <c r="T12" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026 05:45 PM IST</t>
+          <t>31/07/2026 06:01 PM IST</t>
         </is>
       </c>
     </row>
@@ -2027,9 +2076,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E13" s="24" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>EXITED</t>
         </is>
       </c>
       <c r="F13" s="8" t="n">
@@ -2050,7 +2099,7 @@
         <v>2120.56</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>2270.2</v>
+        <v>2233.9</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>2270.2</v>
@@ -2058,22 +2107,34 @@
       <c r="M13" s="8" t="n">
         <v>2120.56</v>
       </c>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="8" t="n">
+        <v>2244.04</v>
+      </c>
       <c r="O13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="7" t="inlineStr"/>
-      <c r="R13" s="7" t="inlineStr"/>
-      <c r="S13" s="7" t="inlineStr"/>
+        <v>-36.3</v>
+      </c>
+      <c r="P13" s="26" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="R13" s="7" t="n">
+        <v>2233.9</v>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>Price crossed below 20 SMA</t>
+        </is>
+      </c>
       <c r="T13" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" s="7" t="inlineStr">
         <is>
-          <t>30/07/2026 05:45 PM IST</t>
+          <t>31/07/2026 06:01 PM IST</t>
         </is>
       </c>
     </row>
@@ -2119,30 +2180,32 @@
         <v>4870.15</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>5168.8</v>
+        <v>5386</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>5168.8</v>
+        <v>5386</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>4870.15</v>
-      </c>
-      <c r="N14" s="5" t="inlineStr"/>
+        <v>5059.84</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>4975.06</v>
+      </c>
       <c r="O14" s="5" t="n">
-        <v>0</v>
+        <v>217.2</v>
       </c>
       <c r="P14" s="25" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="Q14" s="3" t="inlineStr"/>
       <c r="R14" s="3" t="inlineStr"/>
       <c r="S14" s="3" t="inlineStr"/>
       <c r="T14" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026 05:45 PM IST</t>
+          <t>31/07/2026 06:01 PM IST</t>
         </is>
       </c>
     </row>
@@ -2188,30 +2251,32 @@
         <v>229.61</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>248.75</v>
+        <v>256.4599914550781</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>248.75</v>
+        <v>256.4599914550781</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>229.61</v>
-      </c>
-      <c r="N15" s="8" t="inlineStr"/>
+        <v>237.17</v>
+      </c>
+      <c r="N15" s="8" t="n">
+        <v>239.44</v>
+      </c>
       <c r="O15" s="8" t="n">
-        <v>0</v>
+        <v>7.71</v>
       </c>
       <c r="P15" s="25" t="n">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="Q15" s="7" t="inlineStr"/>
       <c r="R15" s="7" t="inlineStr"/>
       <c r="S15" s="7" t="inlineStr"/>
       <c r="T15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15" s="7" t="inlineStr">
         <is>
-          <t>30/07/2026 05:45 PM IST</t>
+          <t>31/07/2026 06:01 PM IST</t>
         </is>
       </c>
     </row>
@@ -2234,9 +2299,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E16" s="24" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="E16" s="27" t="inlineStr">
+        <is>
+          <t>EXITED</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
@@ -2257,7 +2322,7 @@
         <v>520.85</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>553.4</v>
+        <v>523.1</v>
       </c>
       <c r="L16" s="5" t="n">
         <v>553.4</v>
@@ -2265,22 +2330,34 @@
       <c r="M16" s="5" t="n">
         <v>520.85</v>
       </c>
-      <c r="N16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="n">
+        <v>544.37</v>
+      </c>
       <c r="O16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr"/>
+        <v>-30.3</v>
+      </c>
+      <c r="P16" s="26" t="n">
+        <v>-0.0548</v>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>523.1</v>
+      </c>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t>Price crossed below 20 SMA</t>
+        </is>
+      </c>
       <c r="T16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026 05:45 PM IST</t>
+          <t>31/07/2026 06:01 PM IST</t>
         </is>
       </c>
     </row>
@@ -2326,30 +2403,32 @@
         <v>3994.4</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>4422.8</v>
+        <v>4362.10009765625</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>4422.8</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>3994.4</v>
-      </c>
-      <c r="N17" s="8" t="inlineStr"/>
+        <v>4046.69</v>
+      </c>
+      <c r="N17" s="8" t="n">
+        <v>4077.1</v>
+      </c>
       <c r="O17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="25" t="n">
-        <v>0</v>
+        <v>-60.7</v>
+      </c>
+      <c r="P17" s="26" t="n">
+        <v>-0.0137</v>
       </c>
       <c r="Q17" s="7" t="inlineStr"/>
       <c r="R17" s="7" t="inlineStr"/>
       <c r="S17" s="7" t="inlineStr"/>
       <c r="T17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" s="7" t="inlineStr">
         <is>
-          <t>30/07/2026 05:45 PM IST</t>
+          <t>31/07/2026 06:01 PM IST</t>
         </is>
       </c>
     </row>
@@ -2395,30 +2474,32 @@
         <v>3734.72</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>3931.4</v>
+        <v>3938.89990234375</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>3931.4</v>
+        <v>3938.89990234375</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>3734.72</v>
-      </c>
-      <c r="N18" s="5" t="inlineStr"/>
+        <v>3746.49</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>3871.74</v>
+      </c>
       <c r="O18" s="5" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="P18" s="25" t="n">
-        <v>0</v>
+        <v>0.0019</v>
       </c>
       <c r="Q18" s="3" t="inlineStr"/>
       <c r="R18" s="3" t="inlineStr"/>
       <c r="S18" s="3" t="inlineStr"/>
       <c r="T18" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026 05:45 PM IST</t>
+          <t>31/07/2026 06:01 PM IST</t>
         </is>
       </c>
     </row>
@@ -2464,30 +2545,32 @@
         <v>40.12</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>43</v>
+        <v>43.02000045776367</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>43</v>
+        <v>43.02000045776367</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>40.12</v>
-      </c>
-      <c r="N19" s="8" t="inlineStr"/>
+        <v>40.37</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>42.81</v>
+      </c>
       <c r="O19" s="8" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P19" s="25" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="Q19" s="7" t="inlineStr"/>
       <c r="R19" s="7" t="inlineStr"/>
       <c r="S19" s="7" t="inlineStr"/>
       <c r="T19" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U19" s="7" t="inlineStr">
         <is>
-          <t>30/07/2026 05:45 PM IST</t>
+          <t>31/07/2026 06:01 PM IST</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2616,7 @@
         <v>262.3</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>304.15</v>
+        <v>287.1099853515625</v>
       </c>
       <c r="L20" s="5" t="n">
         <v>304.15</v>
@@ -2541,22 +2624,24 @@
       <c r="M20" s="5" t="n">
         <v>262.3</v>
       </c>
-      <c r="N20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="n">
+        <v>274.57</v>
+      </c>
       <c r="O20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="25" t="n">
-        <v>0</v>
+        <v>-17.04</v>
+      </c>
+      <c r="P20" s="26" t="n">
+        <v>-0.056</v>
       </c>
       <c r="Q20" s="3" t="inlineStr"/>
       <c r="R20" s="3" t="inlineStr"/>
       <c r="S20" s="3" t="inlineStr"/>
       <c r="T20" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026 05:45 PM IST</t>
+          <t>31/07/2026 06:01 PM IST</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2687,7 @@
         <v>1767.63</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>1882.2</v>
+        <v>1882</v>
       </c>
       <c r="L21" s="8" t="n">
         <v>1882.2</v>
@@ -2610,22 +2695,24 @@
       <c r="M21" s="8" t="n">
         <v>1767.63</v>
       </c>
-      <c r="N21" s="8" t="inlineStr"/>
+      <c r="N21" s="8" t="n">
+        <v>1844.46</v>
+      </c>
       <c r="O21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="25" t="n">
-        <v>0</v>
+        <v>-0.2</v>
+      </c>
+      <c r="P21" s="26" t="n">
+        <v>-0.0001</v>
       </c>
       <c r="Q21" s="7" t="inlineStr"/>
       <c r="R21" s="7" t="inlineStr"/>
       <c r="S21" s="7" t="inlineStr"/>
       <c r="T21" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21" s="7" t="inlineStr">
         <is>
-          <t>30/07/2026 05:45 PM IST</t>
+          <t>31/07/2026 06:01 PM IST</t>
         </is>
       </c>
     </row>
@@ -2671,30 +2758,32 @@
         <v>633.66</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>678</v>
+        <v>679.4500122070312</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>678</v>
+        <v>679.4500122070312</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>633.66</v>
-      </c>
-      <c r="N22" s="5" t="inlineStr"/>
+        <v>635.6</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>664.61</v>
+      </c>
       <c r="O22" s="5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P22" s="25" t="n">
-        <v>0</v>
+        <v>0.0021</v>
       </c>
       <c r="Q22" s="3" t="inlineStr"/>
       <c r="R22" s="3" t="inlineStr"/>
       <c r="S22" s="3" t="inlineStr"/>
       <c r="T22" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026 05:45 PM IST</t>
+          <t>31/07/2026 06:01 PM IST</t>
         </is>
       </c>
     </row>
@@ -2717,9 +2806,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>PENDING ENTRY</t>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F23" s="8" t="n">
@@ -2728,19 +2817,33 @@
       <c r="G23" s="7" t="n">
         <v>28.41</v>
       </c>
-      <c r="H23" s="7" t="inlineStr"/>
-      <c r="I23" s="8" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>1273.9</v>
+      </c>
       <c r="J23" s="8" t="n">
-        <v>1176.46</v>
+        <v>1188.67</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>1261.7</v>
-      </c>
-      <c r="L23" s="8" t="inlineStr"/>
-      <c r="M23" s="8" t="inlineStr"/>
+        <v>1273.9</v>
+      </c>
+      <c r="L23" s="8" t="n">
+        <v>1273.9</v>
+      </c>
+      <c r="M23" s="8" t="n">
+        <v>1188.67</v>
+      </c>
       <c r="N23" s="8" t="inlineStr"/>
-      <c r="O23" s="8" t="inlineStr"/>
-      <c r="P23" s="9" t="inlineStr"/>
+      <c r="O23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q23" s="7" t="inlineStr"/>
       <c r="R23" s="7" t="inlineStr"/>
       <c r="S23" s="7" t="inlineStr"/>
@@ -2749,7 +2852,7 @@
       </c>
       <c r="U23" s="7" t="inlineStr">
         <is>
-          <t>30/07/2026 05:48 PM IST</t>
+          <t>31/07/2026 06:01 PM IST</t>
         </is>
       </c>
     </row>
@@ -2772,9 +2875,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>PENDING ENTRY</t>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
@@ -2783,19 +2886,33 @@
       <c r="G24" s="3" t="n">
         <v>9.289999999999999</v>
       </c>
-      <c r="H24" s="3" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>167.5</v>
+      </c>
       <c r="J24" s="5" t="n">
-        <v>138.96</v>
+        <v>139.63</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>166.84</v>
-      </c>
-      <c r="L24" s="5" t="inlineStr"/>
-      <c r="M24" s="5" t="inlineStr"/>
+        <v>167.5</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>167.5</v>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>139.63</v>
+      </c>
       <c r="N24" s="5" t="inlineStr"/>
-      <c r="O24" s="5" t="inlineStr"/>
-      <c r="P24" s="6" t="inlineStr"/>
+      <c r="O24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q24" s="3" t="inlineStr"/>
       <c r="R24" s="3" t="inlineStr"/>
       <c r="S24" s="3" t="inlineStr"/>
@@ -2804,7 +2921,7 @@
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026 05:48 PM IST</t>
+          <t>31/07/2026 06:01 PM IST</t>
         </is>
       </c>
     </row>
@@ -2827,9 +2944,9 @@
           <t>Touch &amp; Bounce</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>PENDING ENTRY</t>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F25" s="8" t="n">
@@ -2838,19 +2955,33 @@
       <c r="G25" s="7" t="n">
         <v>9.960000000000001</v>
       </c>
-      <c r="H25" s="7" t="inlineStr"/>
-      <c r="I25" s="8" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>414.95</v>
+      </c>
       <c r="J25" s="8" t="n">
-        <v>385.06</v>
+        <v>385.07</v>
       </c>
       <c r="K25" s="8" t="n">
         <v>414.95</v>
       </c>
-      <c r="L25" s="8" t="inlineStr"/>
-      <c r="M25" s="8" t="inlineStr"/>
+      <c r="L25" s="8" t="n">
+        <v>414.95</v>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>385.07</v>
+      </c>
       <c r="N25" s="8" t="inlineStr"/>
-      <c r="O25" s="8" t="inlineStr"/>
-      <c r="P25" s="9" t="inlineStr"/>
+      <c r="O25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q25" s="7" t="inlineStr"/>
       <c r="R25" s="7" t="inlineStr"/>
       <c r="S25" s="7" t="inlineStr"/>
@@ -2859,7 +2990,502 @@
       </c>
       <c r="U25" s="7" t="inlineStr">
         <is>
-          <t>30/07/2026 05:48 PM IST</t>
+          <t>31/07/2026 06:01 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>AWL</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>189.44</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="n">
+        <v>174.49</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>189.44</v>
+      </c>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="6" t="inlineStr"/>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr"/>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>31/07/2026 06:05 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>166.18</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="8" t="inlineStr"/>
+      <c r="J27" s="8" t="n">
+        <v>154.5</v>
+      </c>
+      <c r="K27" s="8" t="n">
+        <v>166.18</v>
+      </c>
+      <c r="L27" s="8" t="inlineStr"/>
+      <c r="M27" s="8" t="inlineStr"/>
+      <c r="N27" s="8" t="inlineStr"/>
+      <c r="O27" s="8" t="inlineStr"/>
+      <c r="P27" s="9" t="inlineStr"/>
+      <c r="Q27" s="7" t="inlineStr"/>
+      <c r="R27" s="7" t="inlineStr"/>
+      <c r="S27" s="7" t="inlineStr"/>
+      <c r="T27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="7" t="inlineStr">
+        <is>
+          <t>31/07/2026 06:05 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>BALKRISIND</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>2473.5</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>83.25</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="n">
+        <v>2223.74</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>2473.5</v>
+      </c>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="6" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr"/>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>31/07/2026 06:05 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>BLUEDART</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>5160.3</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>110.62</v>
+      </c>
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="8" t="inlineStr"/>
+      <c r="J29" s="8" t="n">
+        <v>4828.44</v>
+      </c>
+      <c r="K29" s="8" t="n">
+        <v>5160.3</v>
+      </c>
+      <c r="L29" s="8" t="inlineStr"/>
+      <c r="M29" s="8" t="inlineStr"/>
+      <c r="N29" s="8" t="inlineStr"/>
+      <c r="O29" s="8" t="inlineStr"/>
+      <c r="P29" s="9" t="inlineStr"/>
+      <c r="Q29" s="7" t="inlineStr"/>
+      <c r="R29" s="7" t="inlineStr"/>
+      <c r="S29" s="7" t="inlineStr"/>
+      <c r="T29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="7" t="inlineStr">
+        <is>
+          <t>31/07/2026 06:05 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>IGIL</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>353.45</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="n">
+        <v>317.05</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>353.45</v>
+      </c>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="6" t="inlineStr"/>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr"/>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>31/07/2026 06:05 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>JKTYRE</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>399.75</v>
+      </c>
+      <c r="G31" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="8" t="inlineStr"/>
+      <c r="J31" s="8" t="n">
+        <v>369.76</v>
+      </c>
+      <c r="K31" s="8" t="n">
+        <v>399.75</v>
+      </c>
+      <c r="L31" s="8" t="inlineStr"/>
+      <c r="M31" s="8" t="inlineStr"/>
+      <c r="N31" s="8" t="inlineStr"/>
+      <c r="O31" s="8" t="inlineStr"/>
+      <c r="P31" s="9" t="inlineStr"/>
+      <c r="Q31" s="7" t="inlineStr"/>
+      <c r="R31" s="7" t="inlineStr"/>
+      <c r="S31" s="7" t="inlineStr"/>
+      <c r="T31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="7" t="inlineStr">
+        <is>
+          <t>31/07/2026 06:05 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>KEI</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>4999</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>127.07</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="n">
+        <v>4617.79</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>4999</v>
+      </c>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="5" t="inlineStr"/>
+      <c r="P32" s="6" t="inlineStr"/>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr"/>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>31/07/2026 06:05 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>SCI</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>291.45</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="H33" s="7" t="inlineStr"/>
+      <c r="I33" s="8" t="inlineStr"/>
+      <c r="J33" s="8" t="n">
+        <v>264.59</v>
+      </c>
+      <c r="K33" s="8" t="n">
+        <v>291.45</v>
+      </c>
+      <c r="L33" s="8" t="inlineStr"/>
+      <c r="M33" s="8" t="inlineStr"/>
+      <c r="N33" s="8" t="inlineStr"/>
+      <c r="O33" s="8" t="inlineStr"/>
+      <c r="P33" s="9" t="inlineStr"/>
+      <c r="Q33" s="7" t="inlineStr"/>
+      <c r="R33" s="7" t="inlineStr"/>
+      <c r="S33" s="7" t="inlineStr"/>
+      <c r="T33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="7" t="inlineStr">
+        <is>
+          <t>31/07/2026 06:05 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Touch &amp; Bounce</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>PENDING ENTRY</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>1027.4</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr"/>
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="5" t="n">
+        <v>973.83</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>1027.4</v>
+      </c>
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="5" t="inlineStr"/>
+      <c r="N34" s="5" t="inlineStr"/>
+      <c r="O34" s="5" t="inlineStr"/>
+      <c r="P34" s="6" t="inlineStr"/>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr"/>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>31/07/2026 06:05 PM IST</t>
         </is>
       </c>
     </row>
